--- a/Result/profitability/6111.xlsx
+++ b/Result/profitability/6111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7299999999999998</v>
+        <v>-0.6462499999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>33.60375000000001</v>
+        <v>32.42375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7299999999999998</v>
+        <v>-0.7462499999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>37.81375</v>
+        <v>37.35875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-1.64</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0225</v>
+        <v>-0.8812499999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>40.88124999999999</v>
+        <v>40.05625000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.52</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2675</v>
+        <v>-1.26875</v>
       </c>
       <c r="N5" t="n">
-        <v>43.2775</v>
+        <v>41.95</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.05125</v>
+        <v>-0.8299999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>50.07125000000001</v>
+        <v>51.045</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7124999999999997</v>
+        <v>-0.2137499999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>59.22375</v>
+        <v>61.02</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3774999999999997</v>
+        <v>-0.2824999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>68.145</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.08124999999999974</v>
       </c>
       <c r="N10" t="n">
-        <v>78.51875</v>
+        <v>78.51875000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.1812499999999997</v>
       </c>
       <c r="N11" t="n">
-        <v>79.72375</v>
+        <v>79.72375000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.08499999999999976</v>
       </c>
       <c r="N12" t="n">
-        <v>83.83125</v>
+        <v>83.83125000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3203</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2286</v>
+      </c>
+      <c r="E75" t="n">
+        <v>918</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>150</v>
+      </c>
+      <c r="J75" t="n">
+        <v>118</v>
+      </c>
+      <c r="K75" t="n">
+        <v>59</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4524999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.3925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08642911296436706</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.01724137931034486</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-10.62</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2703665987780041</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
